--- a/核心业务测试用例_最终.xlsx
+++ b/核心业务测试用例_最终.xlsx
@@ -422,11 +422,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
@@ -437,7 +437,7 @@
     <col width="53" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="68" customWidth="1" min="13" max="13"/>
+    <col width="76" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1046,7 +1046,7 @@
     <row r="10" ht="51.2" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CORE-BOOK-003</t>
+          <t>CORE-BOOK-004</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1110,15 +1110,15 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="47.2" customHeight="1">
+    <row r="11" ht="57.6" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CORE-BOOK-004</t>
+          <t>CORE-BOOK-005</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>继续添加服务</t>
+          <t>继续添加服务入口与单选限制</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1. 选择服务并进入日期时间；2. 选择日期时间；3. 点击继续添加服务；4. 回到服务选择并选择第二个服务</t>
+          <t>1. 选择服务并进入日期时间；2. 选择日期时间；3. 点击继续添加服务；4. 校验回到服务选择；5. 再选一个服务并校验单选</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>页面回到服务选择步骤，可继续选择第二个服务，日期时间选择不被丢失</t>
+          <t>页面回到服务选择步骤；当前站点服务选择为单选，不能同时保留两个服务</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1173,14 +1173,14 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>AI 赋能生成；对应 test_add_another_service_returns_to_service_step</t>
+          <t>AI 赋能生成；对应 test_add_another_service_returns_to_service_step；多服务同单受站点单选限制</t>
         </is>
       </c>
     </row>
     <row r="12" ht="33.6" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CORE-BOOK-005</t>
+          <t>CORE-BOOK-006</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
     <row r="13" ht="43.2" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>CORE-BOOK-006</t>
+          <t>CORE-BOOK-007</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1. 进入预约确认/结算页；2. 点击服务行 x；3. 校验服务被移除</t>
+          <t>1. 进入预约确认/结算页；2. 点击结算页服务行 x；3. 校验服务被移除</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1311,20 +1311,20 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="34.4" customHeight="1">
+    <row r="14" ht="35.2" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>CORE-PAY-001</t>
+          <t>CORE-BOOK-008</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>购物车金额与应付金额一致</t>
+          <t>选择不同服务地点</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>支付</t>
+          <t>预约</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1349,49 +1349,49 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>商品：Laser hair removal - Brazilian；金额：234</t>
+          <t>服务地点：Toowong / Sunnypark</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1. 商品加入购物车；2. 进入结算；3. 校验应付金额</t>
+          <t>1. 进入预约流程；2. 选择服务；3. 校验地点选择；4. 选择不同地点后进入日期时间</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>结算页应付金额显示 $ 234，与购物车小计一致</t>
+          <t>服务地点可选且选择后日期时间/结算信息随之更新</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>金额计算</t>
+          <t>预约地点</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>已自动化</t>
+          <t>待执行</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>AI 赋能生成；对应 test_checkout_amount_calculation</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="40.8" customHeight="1">
+          <t>AI 赋能生成；当前未纳入稳定默认回归</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>CORE-PAY-002</t>
+          <t>CORE-BOOK-009</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>当前 Web 仅 ATM 支付</t>
+          <t>选择上午/下午时段</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>支付</t>
+          <t>预约</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1401,64 +1401,64 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>等价类划分</t>
+          <t>边界值分析</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>已登录会员账号并进入结算页</t>
+          <t>已登录会员账号并进入日期时间步骤</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>支付方式候选</t>
+          <t>09:30、12:30、17:00</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1. 进入结算页；2. 列出支付方式；3. 校验 ATM 为唯一选项</t>
+          <t>1. 选择日期；2. 选择最早/午间/最晚时段；3. 校验时间选择</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>支付方式仅 ATM，符合到店支付配置</t>
+          <t>上午、下午、最晚可约时段均可选择并正确展示结束时间</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>支付方式</t>
+          <t>预约时段</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>已自动化</t>
+          <t>待执行</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>AI 赋能生成；对应 test_checkout_payment_method_is_atm_only</t>
+          <t>AI 赋能生成；当前未纳入稳定默认回归</t>
         </is>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>CORE-PAY-003</t>
+          <t>CORE-BOOK-010</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>支付成功</t>
+          <t>跨月日期选择</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>支付</t>
+          <t>预约</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1468,114 +1468,1186 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>场景法</t>
+          <t>边界值分析</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>已接入 CMS 支付沙箱或模拟网关</t>
+          <t>已登录会员账号并进入日期时间步骤</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>使用测试支付凭据</t>
+          <t>当月最后一天、下月第一天</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1. 提交订单；2. 完成 ATM/模拟支付；3. 校验订单状态为已支付</t>
+          <t>1. 翻到下一月；2. 选择跨月日期；3. 校验日期时间</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>支付成功，订单状态更新为已支付</t>
+          <t>跨月日期可正常选择，预约时间显示正确</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>支付成功</t>
+          <t>预约日历</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>环境受限</t>
+          <t>待执行</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>AI 赋能生成；当前站点无 CMS，无法端到端执行</t>
+          <t>AI 赋能生成；当前未纳入稳定默认回归</t>
         </is>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>CORE-BOOK-011</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>已约时段不可重复选择</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>预约</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>错误猜测</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>测试账号已有同一时段预约</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>同一服务、同一日期时间</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1. 选择已约时段；2. 校验时段状态；3. 尝试提交</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>已约时段不可选或提交时被系统拦截</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>预约冲突</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>环境受限</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>AI 赋能生成；依赖真实预约环境</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>CORE-BOOK-012</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>服务时长与时段冲突校验</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>预约</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>判定表</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>已登录会员账号并进入日期时间步骤</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>30 分钟/60 分钟/90 分钟服务</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1. 选择长时服务；2. 选择临近时段；3. 校验是否提示冲突</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>时段选择会考虑服务时长，冲突时给出提示</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>预约冲突</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>AI 赋能生成；当前未纳入稳定默认回归</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>CORE-BOOK-013</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>预约联系人信息预填</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>预约</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>等价类划分</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>已登录会员账号并进入结算确认页</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>会员姓名、手机、邮箱</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入预约确认；2. 校验联系人字段；3. 修改字段</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>会员联系人信息自动预填且可修改</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>预约确认</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>AI 赋能生成；当前未纳入稳定默认回归</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>CORE-BOOK-014</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>未勾选条款确认预约拦截</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>预约</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>判定表</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>已登录会员账号并进入预约确认页</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>条款：不勾选</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1. 不勾选条款；2. 尝试提交预约；3. 校验提示</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>系统拦截提交并提示需阅读同意条款</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>预约确认</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>AI 赋能生成；当前未纳入稳定默认回归</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>CORE-BOOK-015</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>预约提交成功生成订单</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>预约</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>场景法</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>BOOKING_SUBMIT_ALLOWED=true，测试环境允许真实预约</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>完整预约联系人、条款、时间</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>1. 完成预约；2. 提交；3. 校验预约完成/订单生成</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>预约成功并生成可查询订单</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>预约提交</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>条件执行</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>AI 赋能生成；真实提交需显式开启环境开关</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="34.4" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>CORE-PAY-001</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>购物车金额与应付金额一致</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>支付</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>等价类划分</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>已登录会员账号</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>商品：Laser hair removal - Brazilian；金额：234</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1. 商品加入购物车；2. 进入结算；3. 校验应付金额</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>结算页应付金额显示 $ 234，与购物车小计一致</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>金额计算</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>已自动化</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>AI 赋能生成；对应 test_checkout_amount_calculation</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="40.8" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>CORE-PAY-002</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>当前 Web 仅 ATM 支付</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>支付</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>等价类划分</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>已登录会员账号并进入结算页</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>支付方式候选</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入结算页；2. 列出支付方式；3. 校验 ATM 为唯一选项</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>支付方式仅 ATM，符合到店支付配置</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>支付方式</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>已自动化</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>AI 赋能生成；对应 test_checkout_payment_method_is_atm_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>CORE-PAY-003</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>支付成功</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>支付</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>场景法</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>已接入 CMS 支付沙箱或模拟网关</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>使用测试支付凭据</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1. 提交订单；2. 完成 ATM/模拟支付；3. 校验订单状态为已支付</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>支付成功，订单状态更新为已支付</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>支付成功</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>环境受限</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>AI 赋能生成；当前站点无 CMS，无法端到端执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
           <t>CORE-PAY-004</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>支付失败</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>支付</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>错误猜测</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>已接入 CMS 支付沙箱或模拟网关</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>错误支付凭据/余额不足</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>1. 提交订单；2. 模拟支付失败；3. 校验订单保持待付款</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>支付失败，订单不更新为已支付，页面提示失败</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>支付失败</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>环境受限</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>AI 赋能生成；当前站点无 CMS，无法端到端执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>CORE-PAY-005</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>空购物车进入结算</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>支付</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>边界值分析</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>已登录会员账号</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>购物车为空</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1. 打开结算页；2. 校验空购物车提示</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>不展示可提交订单，金额为 0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>购物车结算</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>AI 赋能生成；当前未纳入稳定默认回归</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>CORE-PAY-006</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>多商品金额汇总</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>支付</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>等价类划分</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>已登录会员账号</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>商品单价：234、999</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>1. 加入多个商品；2. 进入结算；3. 校验总金额</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>应付金额等于各商品小计之和</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>金额计算</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>AI 赋能生成；当前未纳入稳定默认回归</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>CORE-PAY-007</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>商品数量边界</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>支付</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>边界值分析</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>已登录会员账号</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>数量：1、最大库存、0、负数</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>1. 修改数量；2. 加入购物车；3. 校验数量和小计</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>0/负数不可提交，合法数量按数量计算小计</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>金额计算</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>AI 赋能生成；当前未纳入稳定默认回归</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>CORE-PAY-008</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Cash Dollar 抵扣金额</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>支付</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>判定表</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>测试账号有可用 Cash Dollar</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Cash Dollar：10</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入结算；2. 输入抵扣金额；3. 校验应付金额</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>应付金额按抵扣金额减少且不小于 0</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>金额计算</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>环境受限</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>AI 赋能生成；依赖测试账号购物金数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>CORE-PAY-009</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>ATM 到店支付提交订单</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>支付</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>场景法</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>已登录会员账号且订单可提交</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>支付方式：ATM</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>1. 进入结算；2. 选择 ATM；3. 勾选条款；4. 提交订单</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>订单提交成功，状态为待付款，支付方式为 ATM</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>订单提交</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>条件执行</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>AI 赋能生成；真实提交需测试环境允许下单</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>CORE-PAY-010</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>订单待付款状态</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>支付</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>状态迁移</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>已创建 ATM 订单</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>订单状态</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>1. 提交 ATM 订单；2. 进入订单详情；3. 校验状态</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>订单显示待付款，付款方式为 ATM</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>订单状态</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>环境受限</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>AI 赋能生成；依赖真实订单数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>CORE-PAY-011</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>重复提交同一订单拦截</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>支付</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>错误猜测</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>测试环境允许创建订单</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>同一订单连续提交</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>1. 提交订单；2. 再次提交同一订单；3. 校验重复提示</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>系统阻止重复提交或提示订单已存在</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>订单提交</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>环境受限</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>AI 赋能生成；依赖真实订单环境</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>CORE-PAY-012</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>订单金额精度校验</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>支付</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>边界值分析</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>已登录会员账号</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>金额含两位小数</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>1. 构造含小数金额；2. 进入结算；3. 校验金额精度</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>金额保留两位小数，计算无精度误差</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>金额计算</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>AI 赋能生成；当前未纳入稳定默认回归</t>
         </is>
       </c>
     </row>
